--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,84 +476,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -568,106 +568,106 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -682,54 +682,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,44 +749,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -806,44 +806,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,19 +863,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,44 +920,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,19 +977,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,44 +1034,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,49 +1081,49 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1138,49 +1138,49 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1309,49 +1309,49 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,49 +1366,49 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1502,32 +1502,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,19 +1547,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,39 +1661,39 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1730,7 +1730,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,39 +1775,39 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1822,44 +1822,44 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1901,27 +1901,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1941,49 +1941,49 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,44 +1993,44 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2072,32 +2072,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,29 +2107,29 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,44 +2174,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,29 +2221,29 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,44 +2288,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,19 +2345,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,44 +2402,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,39 +2459,39 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,12 +2528,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,39 +2573,39 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,39 +2630,39 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,44 +2687,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,39 +2744,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,49 +2791,49 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,49 +2848,49 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,86 +2905,86 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,39 +3029,39 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3071,59 +3071,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,44 +3143,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,29 +3190,29 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3257,19 +3257,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3314,44 +3314,44 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,54 +3361,54 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3428,39 +3428,39 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3485,34 +3485,34 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3554,27 +3554,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,32 +3611,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3646,44 +3646,44 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3725,22 +3725,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3782,22 +3782,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,32 +3839,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3884,39 +3884,39 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3941,34 +3941,34 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3988,49 +3988,49 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4067,32 +4067,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4102,44 +4102,44 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4181,27 +4181,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4216,54 +4216,54 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4283,44 +4283,44 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4340,44 +4340,44 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4397,39 +4397,39 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4439,116 +4439,116 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4558,49 +4558,49 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4615,49 +4615,49 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4694,27 +4694,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4729,54 +4729,54 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4786,54 +4786,54 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4843,49 +4843,49 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4900,49 +4900,49 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4979,32 +4979,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5024,39 +5024,39 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5081,39 +5081,39 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5138,44 +5138,44 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5195,19 +5195,19 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5217,17 +5217,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5252,44 +5252,44 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5321,27 +5321,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5378,27 +5378,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5435,32 +5435,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5470,49 +5470,49 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5527,54 +5527,54 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5584,49 +5584,49 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5641,49 +5641,49 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5720,27 +5720,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5777,32 +5777,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5812,49 +5812,49 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5869,49 +5869,49 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5948,32 +5948,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5983,54 +5983,54 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6062,32 +6062,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6119,32 +6119,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6176,12 +6176,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6191,17 +6191,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6233,27 +6233,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6290,55 +6290,112 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,96 +521,96 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -625,106 +625,106 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -739,54 +739,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,44 +806,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -863,44 +863,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,19 +920,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,44 +977,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,19 +1034,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,49 +1138,49 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1195,49 +1195,49 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,49 +1366,49 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,49 +1423,49 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1502,27 +1502,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1559,32 +1559,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,19 +1604,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,44 +1661,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,39 +1718,39 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1787,7 +1787,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,39 +1832,39 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1879,44 +1879,44 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1958,27 +1958,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1998,49 +1998,49 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,44 +2050,44 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2129,32 +2129,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,29 +2164,29 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2231,44 +2231,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,29 +2278,29 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,44 +2345,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,19 +2402,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,44 +2459,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,39 +2516,39 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2585,12 +2585,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,39 +2630,39 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,39 +2687,39 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,44 +2744,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,39 +2801,39 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,49 +2848,49 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,49 +2905,49 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,86 +2962,86 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,39 +3086,39 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3128,59 +3128,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3200,44 +3200,44 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,29 +3247,29 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3314,19 +3314,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3371,44 +3371,44 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,54 +3418,54 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3485,39 +3485,39 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3542,34 +3542,34 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3611,27 +3611,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3668,32 +3668,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,44 +3703,44 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3782,22 +3782,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3839,22 +3839,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3896,32 +3896,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3941,39 +3941,39 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3998,34 +3998,34 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4045,49 +4045,49 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4124,32 +4124,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4159,44 +4159,44 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4238,27 +4238,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4273,54 +4273,54 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4340,44 +4340,44 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4397,44 +4397,44 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4454,39 +4454,39 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4496,116 +4496,116 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4615,49 +4615,49 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4672,49 +4672,49 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4751,27 +4751,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4786,54 +4786,54 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4843,54 +4843,54 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4900,49 +4900,49 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4957,49 +4957,49 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5036,32 +5036,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5081,39 +5081,39 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5138,39 +5138,39 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5195,44 +5195,44 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5252,19 +5252,19 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5274,17 +5274,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5309,44 +5309,44 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5378,27 +5378,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5435,27 +5435,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5492,32 +5492,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5527,49 +5527,49 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5584,54 +5584,54 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5641,49 +5641,49 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5698,49 +5698,49 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5777,27 +5777,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5834,32 +5834,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5869,49 +5869,49 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5926,49 +5926,49 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6005,32 +6005,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6040,54 +6040,54 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6119,32 +6119,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6176,32 +6176,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6233,12 +6233,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6248,17 +6248,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6290,27 +6290,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6347,55 +6347,112 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,54 +511,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,96 +578,96 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -682,106 +682,106 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -796,54 +796,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,44 +863,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -920,44 +920,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,19 +977,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,44 +1034,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,44 +1148,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,49 +1195,49 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1252,49 +1252,49 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,49 +1423,49 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,49 +1480,49 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1559,27 +1559,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1616,32 +1616,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,19 +1661,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,44 +1718,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,39 +1775,39 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1844,7 +1844,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1889,39 +1889,39 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,44 +1936,44 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2015,27 +2015,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2055,49 +2055,49 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,44 +2107,44 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2186,32 +2186,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,29 +2221,29 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,44 +2288,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,29 +2335,29 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,44 +2402,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,19 +2459,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,44 +2516,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,39 +2573,39 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2642,12 +2642,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,39 +2687,39 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,39 +2744,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,44 +2801,44 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,39 +2858,39 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,49 +2905,49 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,49 +2962,49 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3019,86 +3019,86 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,39 +3143,39 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3185,59 +3185,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3257,44 +3257,44 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,29 +3304,29 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3371,19 +3371,19 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3428,44 +3428,44 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,54 +3475,54 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3542,39 +3542,39 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3599,34 +3599,34 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3668,27 +3668,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3725,32 +3725,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,44 +3760,44 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,22 +3839,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3896,22 +3896,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3953,32 +3953,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3998,39 +3998,39 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4055,34 +4055,34 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4102,49 +4102,49 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4181,32 +4181,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4216,44 +4216,44 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4295,27 +4295,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4330,54 +4330,54 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4397,44 +4397,44 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4454,44 +4454,44 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4511,39 +4511,39 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4553,116 +4553,116 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4672,49 +4672,49 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4729,49 +4729,49 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4808,27 +4808,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4843,54 +4843,54 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4900,54 +4900,54 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4957,49 +4957,49 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5014,49 +5014,49 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5093,32 +5093,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5138,39 +5138,39 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5195,39 +5195,39 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5252,44 +5252,44 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5309,19 +5309,19 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5331,17 +5331,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5366,44 +5366,44 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5435,27 +5435,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5492,27 +5492,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5549,32 +5549,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5584,49 +5584,49 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5641,54 +5641,54 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5698,49 +5698,49 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5755,49 +5755,49 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5834,27 +5834,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5891,32 +5891,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5926,49 +5926,49 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5983,49 +5983,49 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6062,32 +6062,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6097,54 +6097,54 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6176,32 +6176,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6233,32 +6233,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6290,12 +6290,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6305,17 +6305,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6347,27 +6347,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6404,55 +6404,112 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -511,54 +511,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,44 +578,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,121 +625,121 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,54 +749,54 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,54 +806,54 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,44 +863,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,54 +910,54 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,44 +977,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,44 +1034,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1160,32 +1160,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,44 +1205,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,54 +1252,54 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,39 +1319,39 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,49 +1366,49 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,49 +1480,49 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,39 +1547,39 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,49 +1594,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1673,32 +1673,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,44 +1718,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,44 +1775,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1844,22 +1844,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1889,39 +1889,39 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,39 +1946,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,49 +1993,49 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,49 +2050,49 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,44 +2107,44 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,44 +2174,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,54 +2221,54 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,54 +2278,54 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,54 +2335,54 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,54 +2392,54 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,54 +2449,54 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,32 +2528,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2573,44 +2573,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2642,32 +2642,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,39 +2687,39 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,19 +2744,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2766,17 +2766,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,39 +2801,39 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,54 +2858,54 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,44 +2915,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,29 +2962,29 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,19 +3029,19 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,54 +3086,54 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,96 +3143,96 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3242,116 +3242,116 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,54 +3361,54 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,29 +3418,29 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3485,44 +3485,44 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,54 +3532,54 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,54 +3589,54 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3656,19 +3656,19 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3678,17 +3678,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3713,39 +3713,39 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3782,32 +3782,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,54 +3817,54 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,44 +3874,44 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3953,22 +3953,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4010,32 +4010,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4055,44 +4055,44 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4112,39 +4112,39 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4159,49 +4159,49 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4216,54 +4216,54 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4273,54 +4273,54 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4330,49 +4330,49 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4387,54 +4387,54 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4444,54 +4444,54 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4511,19 +4511,19 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4533,22 +4533,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4568,101 +4568,101 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4682,54 +4682,54 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4739,44 +4739,44 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4796,34 +4796,34 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4843,49 +4843,49 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4900,54 +4900,54 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4967,44 +4967,44 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5024,44 +5024,44 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5081,39 +5081,39 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5128,54 +5128,54 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5195,44 +5195,44 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5252,39 +5252,39 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5309,44 +5309,44 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5366,44 +5366,44 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5423,44 +5423,44 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5480,44 +5480,44 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5549,27 +5549,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5606,32 +5606,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5641,44 +5641,44 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5720,32 +5720,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5777,32 +5777,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5834,22 +5834,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5869,49 +5869,49 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5948,32 +5948,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5983,54 +5983,54 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6062,22 +6062,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6097,54 +6097,54 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6154,54 +6154,54 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6211,44 +6211,44 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6290,32 +6290,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6347,32 +6347,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6404,32 +6404,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6461,55 +6461,169 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>조사총괄과</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -511,44 +511,44 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,22 +590,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,54 +625,54 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,54 +682,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,96 +749,96 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -853,106 +853,106 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -967,54 +967,54 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,44 +1034,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,19 +1148,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,44 +1205,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,19 +1262,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,44 +1319,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,49 +1366,49 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,49 +1423,49 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1502,27 +1502,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1559,27 +1559,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,49 +1594,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,49 +1651,49 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1730,27 +1730,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1787,32 +1787,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,19 +1832,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1889,44 +1889,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,39 +1946,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2015,7 +2015,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,39 +2060,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,44 +2107,44 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2186,27 +2186,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2226,49 +2226,49 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,44 +2278,44 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2357,32 +2357,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,29 +2392,29 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,44 +2459,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,29 +2506,29 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,44 +2573,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,19 +2630,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,44 +2687,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,39 +2744,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2813,12 +2813,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,39 +2858,39 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,39 +2915,39 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,44 +2972,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,39 +3029,39 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3076,49 +3076,49 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3133,49 +3133,49 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,86 +3190,86 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3314,39 +3314,39 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3356,59 +3356,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3428,44 +3428,44 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,29 +3475,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3542,19 +3542,19 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3599,44 +3599,44 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3646,54 +3646,54 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3713,39 +3713,39 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3770,34 +3770,34 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3839,27 +3839,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3896,32 +3896,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3931,44 +3931,44 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4010,22 +4010,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4067,22 +4067,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4124,32 +4124,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4169,39 +4169,39 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4226,34 +4226,34 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4273,49 +4273,49 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4352,32 +4352,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4387,44 +4387,44 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4466,27 +4466,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4501,54 +4501,54 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4568,44 +4568,44 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4625,44 +4625,44 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4682,39 +4682,39 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4724,116 +4724,116 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4843,49 +4843,49 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4900,49 +4900,49 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4979,27 +4979,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5014,54 +5014,54 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5071,54 +5071,54 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5128,49 +5128,49 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5185,49 +5185,49 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5264,32 +5264,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5309,39 +5309,39 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5366,39 +5366,39 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5423,44 +5423,44 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5480,19 +5480,19 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5502,17 +5502,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5537,44 +5537,44 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5606,27 +5606,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5663,27 +5663,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5720,32 +5720,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5755,49 +5755,49 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5812,54 +5812,54 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5869,49 +5869,49 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5926,49 +5926,49 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6005,27 +6005,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6062,32 +6062,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6097,49 +6097,49 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6154,49 +6154,49 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6233,32 +6233,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6268,54 +6268,54 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6347,32 +6347,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6404,32 +6404,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6461,12 +6461,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6476,17 +6476,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6518,27 +6518,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6575,55 +6575,112 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,27 +476,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,34 +521,34 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -568,44 +568,44 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -682,54 +682,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,54 +739,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -806,96 +806,96 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -910,106 +910,106 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1024,54 +1024,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1148,44 +1148,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,19 +1205,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,44 +1262,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,44 +1376,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,49 +1423,49 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,49 +1480,49 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1559,27 +1559,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1616,27 +1616,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,49 +1651,49 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,49 +1708,49 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1787,27 +1787,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1844,32 +1844,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1889,19 +1889,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,44 +1946,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,39 +2003,39 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2072,7 +2072,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2117,39 +2117,39 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,44 +2164,44 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2243,27 +2243,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2283,49 +2283,49 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,44 +2335,44 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2414,32 +2414,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,29 +2449,29 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,44 +2516,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,29 +2563,29 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,44 +2630,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,19 +2687,19 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,44 +2744,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,39 +2801,39 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2870,12 +2870,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,39 +2915,39 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,39 +2972,39 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,44 +3029,44 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,39 +3086,39 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3133,49 +3133,49 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,49 +3190,49 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,86 +3247,86 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3371,39 +3371,39 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3413,59 +3413,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3485,44 +3485,44 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,29 +3532,29 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3656,44 +3656,44 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3703,54 +3703,54 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3770,39 +3770,39 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3827,34 +3827,34 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3896,27 +3896,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3953,32 +3953,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3988,44 +3988,44 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4067,22 +4067,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4124,22 +4124,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4181,32 +4181,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4226,39 +4226,39 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4283,34 +4283,34 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4330,49 +4330,49 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4409,32 +4409,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4444,44 +4444,44 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4523,27 +4523,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4558,54 +4558,54 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4625,44 +4625,44 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4682,44 +4682,44 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4739,39 +4739,39 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4781,116 +4781,116 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4900,49 +4900,49 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4957,49 +4957,49 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5036,27 +5036,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5071,54 +5071,54 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5128,54 +5128,54 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5185,49 +5185,49 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5242,49 +5242,49 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5321,32 +5321,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5366,39 +5366,39 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5423,39 +5423,39 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5480,44 +5480,44 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5537,19 +5537,19 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5559,17 +5559,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5594,44 +5594,44 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5663,27 +5663,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5720,27 +5720,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5777,32 +5777,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5812,49 +5812,49 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5869,54 +5869,54 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5926,49 +5926,49 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5983,49 +5983,49 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6062,27 +6062,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6119,32 +6119,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6154,49 +6154,49 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6211,49 +6211,49 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6290,32 +6290,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6325,54 +6325,54 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6404,32 +6404,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6461,32 +6461,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6518,12 +6518,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6533,17 +6533,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6575,27 +6575,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6632,55 +6632,112 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K111"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
+          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,49 +511,49 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,34 +578,34 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,44 +625,44 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -704,22 +704,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -739,54 +739,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,54 +796,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,96 +863,96 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -967,106 +967,106 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1081,54 +1081,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,44 +1148,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1205,44 +1205,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,19 +1262,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,44 +1319,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,19 +1376,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,49 +1480,49 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1537,49 +1537,49 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1616,27 +1616,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1673,27 +1673,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,49 +1708,49 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,49 +1765,49 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1844,27 +1844,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1901,32 +1901,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,19 +1946,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,44 +2003,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,39 +2060,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2129,7 +2129,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,39 +2174,39 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2221,44 +2221,44 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2300,27 +2300,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2340,49 +2340,49 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,44 +2392,44 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2471,32 +2471,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,29 +2506,29 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,44 +2573,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,29 +2620,29 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2687,44 +2687,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,19 +2744,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,44 +2801,44 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,39 +2858,39 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2927,12 +2927,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,39 +2972,39 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,39 +3029,39 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,44 +3086,44 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,39 +3143,39 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,49 +3190,49 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,49 +3247,49 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,86 +3304,86 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3428,39 +3428,39 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3470,59 +3470,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3542,44 +3542,44 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,29 +3589,29 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3656,19 +3656,19 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3713,44 +3713,44 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,54 +3760,54 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3827,39 +3827,39 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3884,34 +3884,34 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3953,27 +3953,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4010,32 +4010,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4045,44 +4045,44 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4124,22 +4124,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4181,22 +4181,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4238,32 +4238,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4283,39 +4283,39 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4340,34 +4340,34 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4387,49 +4387,49 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4466,32 +4466,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4501,44 +4501,44 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4580,27 +4580,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4615,54 +4615,54 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4682,44 +4682,44 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4739,44 +4739,44 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4796,39 +4796,39 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4838,116 +4838,116 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4957,49 +4957,49 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5014,49 +5014,49 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5093,27 +5093,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5128,54 +5128,54 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5185,54 +5185,54 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5242,49 +5242,49 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5299,49 +5299,49 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5378,32 +5378,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5423,39 +5423,39 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5480,39 +5480,39 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5537,44 +5537,44 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5594,19 +5594,19 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5616,17 +5616,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5651,44 +5651,44 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5720,27 +5720,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5777,27 +5777,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5834,32 +5834,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5869,49 +5869,49 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5926,54 +5926,54 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5983,49 +5983,49 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6040,49 +6040,49 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6119,27 +6119,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6176,32 +6176,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6211,49 +6211,49 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6268,49 +6268,49 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6347,32 +6347,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6382,54 +6382,54 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6461,32 +6461,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6518,32 +6518,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6575,12 +6575,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6590,17 +6590,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6632,27 +6632,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6689,55 +6689,112 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B112" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F112" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
+          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,54 +511,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
+          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,49 +568,49 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -635,34 +635,34 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -682,44 +682,44 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -761,22 +761,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,54 +796,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,54 +853,54 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,96 +920,96 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1024,106 +1024,106 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1138,54 +1138,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,44 +1205,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1262,44 +1262,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,19 +1319,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,44 +1376,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,19 +1433,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,44 +1490,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,49 +1537,49 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,49 +1594,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1673,27 +1673,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1730,27 +1730,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,49 +1765,49 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1822,49 +1822,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1901,27 +1901,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1958,32 +1958,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2003,19 +2003,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,44 +2060,44 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2117,39 +2117,39 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2186,7 +2186,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2231,39 +2231,39 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2278,44 +2278,44 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2357,27 +2357,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2397,49 +2397,49 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,44 +2449,44 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,32 +2528,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,29 +2563,29 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,44 +2630,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,29 +2677,29 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2744,44 +2744,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,19 +2801,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,44 +2858,44 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,39 +2915,39 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2984,12 +2984,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,39 +3029,39 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,39 +3086,39 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,44 +3143,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3200,39 +3200,39 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,49 +3247,49 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,49 +3304,49 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3361,86 +3361,86 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3485,39 +3485,39 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3527,59 +3527,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3599,44 +3599,44 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3646,29 +3646,29 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3713,19 +3713,19 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3770,44 +3770,44 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,54 +3817,54 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3884,39 +3884,39 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3941,34 +3941,34 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4010,27 +4010,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4067,32 +4067,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4102,44 +4102,44 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4181,22 +4181,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4238,22 +4238,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4295,32 +4295,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4340,39 +4340,39 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4397,34 +4397,34 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4444,49 +4444,49 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4523,32 +4523,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4558,44 +4558,44 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4637,27 +4637,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4672,54 +4672,54 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4739,44 +4739,44 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4796,44 +4796,44 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4853,39 +4853,39 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4895,116 +4895,116 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5014,49 +5014,49 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5071,49 +5071,49 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5150,27 +5150,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5185,54 +5185,54 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5242,54 +5242,54 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5299,49 +5299,49 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5356,49 +5356,49 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5435,32 +5435,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5480,39 +5480,39 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5537,39 +5537,39 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5594,44 +5594,44 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5651,19 +5651,19 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5673,17 +5673,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5708,44 +5708,44 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5777,27 +5777,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5834,27 +5834,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5891,32 +5891,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5926,49 +5926,49 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5983,54 +5983,54 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6040,49 +6040,49 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6097,49 +6097,49 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6176,27 +6176,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6233,32 +6233,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6268,49 +6268,49 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6325,49 +6325,49 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6404,32 +6404,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6439,54 +6439,54 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6518,32 +6518,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6575,32 +6575,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6632,12 +6632,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6647,17 +6647,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6689,27 +6689,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6746,55 +6746,112 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>64211</t>
+          <t>66092</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 예비지정 공고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12518</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
+          <t>인공지능(AI)시대의 데이터 혁신 활용 거점 ‘개인정보 이노베이션 존’ 추가 지정</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12520</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -578,101 +578,101 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
+          <t>정부인사 발령(개인정보보호위원회)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12524</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -692,44 +692,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,39 +749,39 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -796,29 +796,29 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,44 +863,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,44 +920,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -977,54 +977,54 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,54 +1034,54 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,121 +1138,121 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,44 +1262,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,54 +1309,54 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1376,44 +1376,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,44 +1490,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,44 +1547,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,54 +1594,54 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1673,32 +1673,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,39 +1718,39 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1765,49 +1765,49 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1822,49 +1822,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1889,39 +1889,39 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1946,39 +1946,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,54 +1993,54 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2060,44 +2060,44 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2117,44 +2117,44 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2174,34 +2174,34 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2243,22 +2243,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2335,49 +2335,49 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2392,29 +2392,29 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2424,17 +2424,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,19 +2459,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,19 +2516,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,44 +2573,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,44 +2630,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,54 +2677,54 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2756,32 +2756,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,54 +2791,54 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,54 +2848,54 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,44 +2915,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,44 +2972,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3041,7 +3041,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3051,22 +3051,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,39 +3086,39 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,39 +3143,39 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3200,44 +3200,44 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3257,101 +3257,101 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3371,39 +3371,39 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3418,121 +3418,121 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3542,44 +3542,44 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3599,111 +3599,111 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3713,44 +3713,44 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3760,54 +3760,54 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,54 +3817,54 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,54 +3874,54 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3936,49 +3936,49 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3988,54 +3988,54 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4055,39 +4055,39 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4112,44 +4112,44 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4159,54 +4159,54 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4216,54 +4216,54 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4273,44 +4273,44 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4352,32 +4352,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4397,44 +4397,44 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4454,44 +4454,44 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4506,39 +4506,39 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4558,54 +4558,54 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4625,44 +4625,44 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4677,49 +4677,49 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4739,44 +4739,44 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4786,54 +4786,54 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4848,49 +4848,49 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4910,101 +4910,101 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5024,44 +5024,44 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5071,111 +5071,111 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5195,39 +5195,39 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5252,44 +5252,44 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5309,44 +5309,44 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5356,44 +5356,44 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5413,54 +5413,54 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5480,44 +5480,44 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5527,54 +5527,54 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5594,44 +5594,44 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5651,44 +5651,44 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5708,56 +5708,56 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>운영지원과</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>조사1과</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>보도자료</t>
@@ -5765,44 +5765,44 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5822,44 +5822,44 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5879,44 +5879,44 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5948,32 +5948,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5983,54 +5983,54 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6062,32 +6062,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6097,54 +6097,54 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6154,54 +6154,54 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6233,27 +6233,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6268,54 +6268,54 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6325,54 +6325,54 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6404,32 +6404,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6461,32 +6461,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6518,32 +6518,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6553,54 +6553,54 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6610,54 +6610,54 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6689,32 +6689,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6746,32 +6746,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6803,55 +6803,226 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>개인정보보호정책과</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>11169</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>조사총괄과</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>13472</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B116" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K116"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>66092</t>
+          <t>67721</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 예비지정 공고</t>
+          <t>청년인턴의 시선으로, 개인정보 정책을 더 가깝게!</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12518</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12526</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,44 +511,44 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-21 10:01:11.083915+09:00</t>
+          <t>2026-09-23 10:00:25.534327+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-21 10:01:11.083915+09:00</t>
+          <t>2026-09-23 10:00:25.534327+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>66082</t>
+          <t>66092</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>인공지능(AI)시대의 데이터 혁신 활용 거점 ‘개인정보 이노베이션 존’ 추가 지정</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 예비지정 공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12520</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12518</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -568,49 +568,49 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:00:31.705975+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:00:31.705975+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>정부인사 발령(개인정보보호위원회)</t>
+          <t>인공지능(AI)시대의 데이터 혁신 활용 거점 ‘개인정보 이노베이션 존’ 추가 지정</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12524</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12520</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,12 +620,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -647,89 +647,89 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>64211</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
+          <t>정부인사 발령(개인정보보호위원회)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12524</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
+          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -739,54 +739,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
+          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,49 +796,49 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -863,34 +863,34 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -910,44 +910,44 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -989,22 +989,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1024,54 +1024,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1081,54 +1081,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1148,96 +1148,96 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1252,106 +1252,106 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,54 +1366,54 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1490,44 +1490,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,19 +1547,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,19 +1661,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,44 +1718,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,49 +1765,49 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1822,49 +1822,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1901,27 +1901,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1958,27 +1958,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,49 +1993,49 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,49 +2050,49 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2129,27 +2129,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2186,32 +2186,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2231,19 +2231,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,44 +2288,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,39 +2345,39 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2414,7 +2414,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,39 +2459,39 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,44 +2506,44 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2585,27 +2585,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2625,49 +2625,49 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2677,44 +2677,44 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2756,32 +2756,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,29 +2791,29 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2858,44 +2858,44 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,29 +2905,29 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,44 +2972,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,19 +3029,19 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,44 +3086,44 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,39 +3143,39 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3212,12 +3212,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3257,39 +3257,39 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3314,39 +3314,39 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3371,44 +3371,44 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3428,39 +3428,39 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3475,49 +3475,49 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3532,49 +3532,49 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,86 +3589,86 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3713,39 +3713,39 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3755,59 +3755,59 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3827,44 +3827,44 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,29 +3874,29 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3941,19 +3941,19 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3998,44 +3998,44 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4045,54 +4045,54 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4112,39 +4112,39 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4169,34 +4169,34 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4238,27 +4238,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4295,32 +4295,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4330,44 +4330,44 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4409,22 +4409,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4466,22 +4466,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4523,32 +4523,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4568,39 +4568,39 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4625,34 +4625,34 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4672,49 +4672,49 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4751,32 +4751,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4786,44 +4786,44 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4865,27 +4865,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4900,54 +4900,54 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4967,44 +4967,44 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5024,44 +5024,44 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5081,39 +5081,39 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5123,116 +5123,116 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5242,49 +5242,49 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5299,49 +5299,49 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5378,27 +5378,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5413,54 +5413,54 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5470,54 +5470,54 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5527,49 +5527,49 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5584,49 +5584,49 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5663,32 +5663,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5708,39 +5708,39 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5765,39 +5765,39 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5822,44 +5822,44 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5879,19 +5879,19 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5901,17 +5901,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5936,44 +5936,44 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6005,27 +6005,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6062,27 +6062,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6119,32 +6119,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6154,49 +6154,49 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6211,54 +6211,54 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6268,49 +6268,49 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6325,49 +6325,49 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6404,27 +6404,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6461,32 +6461,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6496,49 +6496,49 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6553,49 +6553,49 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6632,32 +6632,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6667,54 +6667,54 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6746,32 +6746,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6803,32 +6803,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6860,12 +6860,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6917,27 +6917,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6974,55 +6974,112 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>67721</t>
+          <t>68201</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>청년인턴의 시선으로, 개인정보 정책을 더 가깝게!</t>
+          <t>에이전틱 인공지능(Agentic AI)과 개인정보보호, 민관 협력을 통한 합리적 규율체계 모색</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12526</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12527</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00:25.534327+09:00</t>
+          <t>2026-09-23 16:00:25.481812+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00:25.534327+09:00</t>
+          <t>2026-09-23 16:00:25.481812+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>66092</t>
+          <t>67721</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 예비지정 공고</t>
+          <t>청년인턴의 시선으로, 개인정보 정책을 더 가깝게!</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12518</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12526</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,44 +568,44 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:01:11.083915+09:00</t>
+          <t>2026-09-23 10:00:25.534327+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:01:11.083915+09:00</t>
+          <t>2026-09-23 10:00:25.534327+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>66082</t>
+          <t>66092</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>인공지능(AI)시대의 데이터 혁신 활용 거점 ‘개인정보 이노베이션 존’ 추가 지정</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 예비지정 공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12520</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12518</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,49 +625,49 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-21 10:00:31.705975+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-21 10:00:31.705975+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>정부인사 발령(개인정보보호위원회)</t>
+          <t>인공지능(AI)시대의 데이터 혁신 활용 거점 ‘개인정보 이노베이션 존’ 추가 지정</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12524</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12520</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -704,89 +704,89 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>64211</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
+          <t>정부인사 발령(개인정보보호위원회)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12524</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
+          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -796,54 +796,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
+          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,49 +853,49 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -920,34 +920,34 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -967,44 +967,44 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1046,22 +1046,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1081,54 +1081,54 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1138,54 +1138,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1205,96 +1205,96 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1309,106 +1309,106 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,54 +1423,54 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1490,44 +1490,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1547,44 +1547,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,19 +1604,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,44 +1661,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,19 +1718,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,44 +1775,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,49 +1822,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1879,49 +1879,49 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1958,27 +1958,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2015,27 +2015,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,49 +2050,49 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,49 +2107,49 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2186,27 +2186,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2243,32 +2243,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,19 +2288,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,44 +2345,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,39 +2402,39 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,39 +2516,39 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,44 +2563,44 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2642,27 +2642,27 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2682,49 +2682,49 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2734,44 +2734,44 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2813,32 +2813,32 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,29 +2848,29 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,44 +2915,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,29 +2962,29 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,44 +3029,44 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,44 +3143,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3200,39 +3200,39 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3269,12 +3269,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3314,39 +3314,39 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3371,39 +3371,39 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3428,44 +3428,44 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3485,39 +3485,39 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3532,49 +3532,49 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,49 +3589,49 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3646,86 +3646,86 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3770,39 +3770,39 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3812,59 +3812,59 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3884,44 +3884,44 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3931,29 +3931,29 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3998,19 +3998,19 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4055,44 +4055,44 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4102,54 +4102,54 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4169,39 +4169,39 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4226,34 +4226,34 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4295,27 +4295,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4352,32 +4352,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4387,44 +4387,44 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4466,22 +4466,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4523,22 +4523,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4580,32 +4580,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4625,39 +4625,39 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4682,34 +4682,34 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4729,49 +4729,49 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4808,32 +4808,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4843,44 +4843,44 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4922,27 +4922,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4957,54 +4957,54 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5024,44 +5024,44 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5081,44 +5081,44 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5138,39 +5138,39 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5180,116 +5180,116 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5299,49 +5299,49 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5356,49 +5356,49 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5435,27 +5435,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5470,54 +5470,54 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5527,54 +5527,54 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5584,49 +5584,49 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5641,49 +5641,49 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5720,32 +5720,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5765,39 +5765,39 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5822,39 +5822,39 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5879,44 +5879,44 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5936,19 +5936,19 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5958,17 +5958,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5993,44 +5993,44 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6062,27 +6062,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6119,27 +6119,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6176,32 +6176,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6211,49 +6211,49 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6268,54 +6268,54 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6325,49 +6325,49 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6382,49 +6382,49 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6461,27 +6461,27 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6518,32 +6518,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6553,49 +6553,49 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6610,49 +6610,49 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6689,32 +6689,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6724,54 +6724,54 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6803,32 +6803,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6860,32 +6860,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6917,12 +6917,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6932,17 +6932,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6974,27 +6974,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7031,55 +7031,112 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,32 +476,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>68201</t>
+          <t>71821</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>에이전틱 인공지능(Agentic AI)과 개인정보보호, 민관 협력을 통한 합리적 규율체계 모색</t>
+          <t>국민·기업·정부가 함께 만드는 개인정보 보호 문화… 「2026 개인정보 보호주간」 운영</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12527</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12529</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,19 +521,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-23 16:00:25.481812+09:00</t>
+          <t>2026-09-28 10:00:28.018143+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-23 16:00:25.481812+09:00</t>
+          <t>2026-09-28 10:00:28.018143+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>67721</t>
+          <t>68201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -543,17 +543,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>청년인턴의 시선으로, 개인정보 정책을 더 가깝게!</t>
+          <t>에이전틱 인공지능(Agentic AI)과 개인정보보호, 민관 협력을 통한 합리적 규율체계 모색</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12526</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12527</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -578,44 +578,44 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00:25.534327+09:00</t>
+          <t>2026-09-23 16:00:25.481812+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00:25.534327+09:00</t>
+          <t>2026-09-23 16:00:25.481812+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>66092</t>
+          <t>67721</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 예비지정 공고</t>
+          <t>청년인턴의 시선으로, 개인정보 정책을 더 가깝게!</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12518</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12526</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,44 +625,44 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-21 10:01:11.083915+09:00</t>
+          <t>2026-09-23 10:00:25.534327+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-21 10:01:11.083915+09:00</t>
+          <t>2026-09-23 10:00:25.534327+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>66082</t>
+          <t>66092</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>인공지능(AI)시대의 데이터 혁신 활용 거점 ‘개인정보 이노베이션 존’ 추가 지정</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 예비지정 공고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12520</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12518</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -682,49 +682,49 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-21 10:00:31.705975+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-21 10:00:31.705975+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>정부인사 발령(개인정보보호위원회)</t>
+          <t>인공지능(AI)시대의 데이터 혁신 활용 거점 ‘개인정보 이노베이션 존’ 추가 지정</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12524</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12520</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -761,89 +761,89 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>64211</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
+          <t>정부인사 발령(개인정보보호위원회)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12524</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
+          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -853,54 +853,54 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
+          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,49 +910,49 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -977,34 +977,34 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1024,44 +1024,44 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1103,22 +1103,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1138,54 +1138,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,54 +1195,54 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1262,96 +1262,96 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1366,106 +1366,106 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1480,54 +1480,54 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1547,44 +1547,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1661,19 +1661,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,44 +1718,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,19 +1775,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,44 +1832,44 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1879,49 +1879,49 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1936,49 +1936,49 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2015,27 +2015,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2072,27 +2072,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,49 +2107,49 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,49 +2164,49 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2243,27 +2243,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2300,32 +2300,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2345,19 +2345,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,44 +2402,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,39 +2459,39 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2528,7 +2528,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2573,39 +2573,39 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2620,44 +2620,44 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2699,27 +2699,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2739,49 +2739,49 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2791,44 +2791,44 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2870,32 +2870,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2905,29 +2905,29 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2972,44 +2972,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3019,29 +3019,29 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3086,44 +3086,44 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,19 +3143,19 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3200,44 +3200,44 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3257,39 +3257,39 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3326,12 +3326,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3371,39 +3371,39 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3428,39 +3428,39 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3485,44 +3485,44 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3542,39 +3542,39 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3589,49 +3589,49 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3646,49 +3646,49 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3703,86 +3703,86 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3827,39 +3827,39 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3869,59 +3869,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3941,44 +3941,44 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3988,29 +3988,29 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4055,19 +4055,19 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4112,44 +4112,44 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4159,54 +4159,54 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4226,39 +4226,39 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4283,34 +4283,34 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4352,27 +4352,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4409,32 +4409,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4444,44 +4444,44 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4523,22 +4523,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4580,22 +4580,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4637,32 +4637,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4682,39 +4682,39 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4739,34 +4739,34 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4786,49 +4786,49 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4865,32 +4865,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4900,44 +4900,44 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4979,27 +4979,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5014,54 +5014,54 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5081,44 +5081,44 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5138,44 +5138,44 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5195,39 +5195,39 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5237,116 +5237,116 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5356,49 +5356,49 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5413,49 +5413,49 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5492,27 +5492,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5527,54 +5527,54 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5584,54 +5584,54 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5641,49 +5641,49 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5698,49 +5698,49 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5777,32 +5777,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5822,39 +5822,39 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5879,39 +5879,39 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5936,44 +5936,44 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5993,19 +5993,19 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6015,17 +6015,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6050,44 +6050,44 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6119,27 +6119,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6176,27 +6176,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6233,32 +6233,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6268,49 +6268,49 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6325,54 +6325,54 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6382,49 +6382,49 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6439,49 +6439,49 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6518,27 +6518,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6575,32 +6575,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6610,49 +6610,49 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6667,49 +6667,49 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6746,32 +6746,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6781,54 +6781,54 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6860,32 +6860,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6917,32 +6917,32 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6974,12 +6974,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6989,17 +6989,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7031,27 +7031,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7088,55 +7088,112 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/pipc.xlsx
+++ b/docs/snapshot/downloads/pipc.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>71821</t>
+          <t>71981</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -486,17 +486,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>국민·기업·정부가 함께 만드는 개인정보 보호 문화… 「2026 개인정보 보호주간」 운영</t>
+          <t>개인정보위, 인공지능 혁신을 이끌 글로벌 프라이버시 가드레일 설계</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12529</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12530</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -521,44 +521,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-28 10:00:28.018143+09:00</t>
+          <t>2026-09-28 12:00:25.679262+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-28 10:00:28.018143+09:00</t>
+          <t>2026-09-28 12:00:25.679262+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>68201</t>
+          <t>71821</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>에이전틱 인공지능(Agentic AI)과 개인정보보호, 민관 협력을 통한 합리적 규율체계 모색</t>
+          <t>국민·기업·정부가 함께 만드는 개인정보 보호 문화… 「2026 개인정보 보호주간」 운영</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12527</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12529</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -578,19 +578,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-23 16:00:25.481812+09:00</t>
+          <t>2026-09-28 10:00:28.018143+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-23 16:00:25.481812+09:00</t>
+          <t>2026-09-28 10:00:28.018143+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>67721</t>
+          <t>68201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>청년인턴의 시선으로, 개인정보 정책을 더 가깝게!</t>
+          <t>에이전틱 인공지능(Agentic AI)과 개인정보보호, 민관 협력을 통한 합리적 규율체계 모색</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12526</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12527</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -635,44 +635,44 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00:25.534327+09:00</t>
+          <t>2026-09-23 16:00:25.481812+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00:25.534327+09:00</t>
+          <t>2026-09-23 16:00:25.481812+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>66092</t>
+          <t>67721</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 예비지정 공고</t>
+          <t>청년인턴의 시선으로, 개인정보 정책을 더 가깝게!</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12518</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12526</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,44 +682,44 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-21 10:01:11.083915+09:00</t>
+          <t>2026-09-23 10:00:25.534327+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-21 10:01:11.083915+09:00</t>
+          <t>2026-09-23 10:00:25.534327+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>66082</t>
+          <t>66092</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>인공지능(AI)시대의 데이터 혁신 활용 거점 ‘개인정보 이노베이션 존’ 추가 지정</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 예비지정 공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12520</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12518</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -739,49 +739,49 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-21 10:00:31.705975+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-21 10:00:31.705975+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>정부인사 발령(개인정보보호위원회)</t>
+          <t>인공지능(AI)시대의 데이터 혁신 활용 거점 ‘개인정보 이노베이션 존’ 추가 지정</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12524</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12520</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -818,89 +818,89 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>64211</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
+          <t>정부인사 발령(개인정보보호위원회)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12524</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
+          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -910,54 +910,54 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
+          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -967,49 +967,49 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1034,34 +1034,34 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1081,44 +1081,44 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1195,54 +1195,54 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1252,54 +1252,54 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1319,96 +1319,96 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1423,106 +1423,106 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1537,54 +1537,54 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1604,44 +1604,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1661,44 +1661,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1718,19 +1718,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1775,44 +1775,44 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1832,19 +1832,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1889,44 +1889,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1936,49 +1936,49 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1993,49 +1993,49 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2072,27 +2072,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2129,27 +2129,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2164,49 +2164,49 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2221,49 +2221,49 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2300,27 +2300,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2357,32 +2357,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2402,19 +2402,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2459,44 +2459,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2516,39 +2516,39 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2585,7 +2585,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2630,39 +2630,39 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2677,44 +2677,44 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2756,27 +2756,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2796,49 +2796,49 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2848,44 +2848,44 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2927,32 +2927,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,29 +2962,29 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3029,44 +3029,44 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3076,29 +3076,29 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3143,44 +3143,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3200,19 +3200,19 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3257,44 +3257,44 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3314,39 +3314,39 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-01 1